--- a/data/ratesPerQuantity/Output/Consolidated_RPQ_Report_26Jun.xlsx
+++ b/data/ratesPerQuantity/Output/Consolidated_RPQ_Report_26Jun.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="TC10" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -50,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -418,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -433,387 +428,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>TC10</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E47"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Data Validation Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Total mismatches</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Missing Columns</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Missing in RPT_RPT8107702707903CZ_ratesPerQuantity.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>Extra Rows</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Base/QTY - w/ Lift_10/27-09/28</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>Group Summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Base/QTY - w/ Lift_10/29-09/30</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>Mismatch Details</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Key</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Missing in TC10_Exc_RPQ.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Base %_10/26-09/27</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Base %_10/27-09/28</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Base %_10/28-09/29</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Base %_10/29-09/30</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Base %_10/30-09/31</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>MAF %_10/26-09/27</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>MAF %_10/27-09/28</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>MAF %_10/28-09/29</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>MAF %_10/29-09/30</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>MAF %_10/30-09/31</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>PPA%_10/26-09/27</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>PPA%_10/27-09/28</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>PPA%_10/28-09/29</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>PPA%_10/29-09/30</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>PPA%_10/30-09/31</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>PPL%_10/26-09/27</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>PPL%_10/27-09/28</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>PPL%_10/28-09/29</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>PPL%_10/29-09/30</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>PPL%_10/30-09/31</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>TOTAL/QTY_10/26-09/27</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>TOTAL/QTY_10/27-09/28</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>TOTAL/QTY_10/28-09/29</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>TOTAL/QTY_10/29-09/30</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>TOTAL/QTY_10/30-09/31</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Total%_10/26-09/27</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Total%_10/27-09/28</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Total%_10/28-09/29</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Total%_10/29-09/30</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Total%_10/30-09/31</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Extra in RPT_RPT8107702707903CZ_ratesPerQuantity.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Extra in TC10_Exc_RPQ.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Group</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>NDC11</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Column</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>RPT_RPT8107702707903CZ_ratesPerQuantity.xlsx</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>TC10_Exc_RPQ.xlsx</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Highlighted</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
